--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Servizi cimiteriali.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Servizi cimiteriali.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="163">
   <si>
     <r>
       <t xml:space="preserve">
@@ -581,7 +581,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> alle hh:mm. 
+      <t xml:space="preserve"> alle hh:mm.
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -800,36 +800,8 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> è stata accolta. 
+      <t xml:space="preserve"> è stata accolta.
 Per maggiori informazioni, [visita questo sito](URL).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">La tua richiesta per </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;nome servizio&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> non è stata accolta.
-Per ulteriori informazioni,  [visita questo sito](URL).</t>
     </r>
   </si>
   <si>
@@ -1008,8 +980,8 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve"> è stata accolta.
-Il rilascio della concessione è subordinato al pagamento del canone per cui ti arriverà un messaggio in app con l'avviso di pagamento. 
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Il rilascio della concessione è subordinato al pagamento del canone per cui ti arriverà un messaggio in app con l'avviso di pagamento.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
 Per ulteriori informazioni sulla durata della concessione, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -1143,7 +1115,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> È possibile richiedere la domiciliazione delle rette direttamente sul tuo conto corrente. Per maggiori informazioni, [visita questo sito](URL). 
+      <t xml:space="preserve"> È possibile richiedere la domiciliazione delle rette direttamente sul tuo conto corrente. Per maggiori informazioni, [visita questo sito](URL).
 Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
@@ -1263,8 +1235,8 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
-Se desideri prorogare la tua concessione, scopri come  [visitando questo sito](URL).</t>
+      <t xml:space="preserve">.
+Se desideri prorogare la tua concessione, scopri come [visitando questo sito](URL).</t>
     </r>
   </si>
   <si>
@@ -1426,7 +1398,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve"> È possibile richiedere la domiciliazione delle rette direttamente sul tuo conto corrente. Per maggiori informazioni, [visita questo sito](URL).
-Se hai già pagato o se hai richiesto la domiciliazione sul conto corrente, ignora pure questo messaggio. 
+Se hai già pagato o se hai richiesto la domiciliazione sul conto corrente, ignora pure questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
@@ -1500,7 +1472,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> è scaduta. 
+      <t xml:space="preserve"> è scaduta.
 Per ulteriori informazioni sulla durata della concessione, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -1529,145 +1501,9 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve"> è stata accolta.
-La richiesta è subordinata a un pagamento per la pratica per cui ti arriverà un messaggio in app con l'avviso di pagamento. 
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+La richiesta è subordinata a un pagamento per la pratica per cui ti arriverà un messaggio in app con l'avviso di pagamento.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
 Per ulteriori informazioni, [visita questo sito](URL).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">C'è un avviso da pagare intestato a </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;nome e cognome&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> e relativo a </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;causale&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>Devi pagare:</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;00,00&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> €
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>Entro il:</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;gg/mm/aaaa&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff448844"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>[Se previsto]</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> È possibile richiedere la domiciliazione delle rette direttamente sul tuo conto corrente. Per maggiori informazioni, [visita questo sito](URL). 
-Se hai già pagato o se hai richiesto la domiciliazione sul conto corrente, ignora pure questo messaggio. 
-Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
-In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
   </si>
   <si>
@@ -1701,20 +1537,11 @@
   <si>
     <r>
       <rPr>
-        <b/>
         <family val="2"/>
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>È stato pubblicato il nuovo calendario delle esumazioni ordinarie per:</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> 
+      <t xml:space="preserve">È stato pubblicato il nuovo calendario delle esumazioni ordinarie per:
 </t>
     </r>
     <r>
@@ -1844,7 +1671,7 @@
     <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
-    <t>Disdici richiesta</t>
+    <t>Annulla richiesta</t>
   </si>
   <si>
     <r>
@@ -1864,7 +1691,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -1988,24 +1815,12 @@
     </r>
   </si>
   <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mancato pagamento
 Il seguente messaggio serve a sensibilizzare il cittadino per il mancato pagamento ma non costituisce in alcun modo un avviso a valore legale (i.e. notifica)</t>
   </si>
   <si>
     <t xml:space="preserve">Mancato pagamento
 Il seguente messaggio serve a sensibilizzare il cittadino per il mancato pagamento ma non costituisce in alcun modo un avviso a valore legale (i.e. notifica).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
   </si>
 </sst>
 </file>
@@ -2980,173 +2795,173 @@
         <v>109</v>
       </c>
       <c r="I5" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="J5" s="34" t="s">
         <v>110</v>
-      </c>
-      <c r="J5" s="34" t="s">
-        <v>111</v>
       </c>
       <c r="K5" s="34" t="s">
         <v>106</v>
       </c>
       <c r="L5" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="M5" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="M5" s="34" t="s">
+      <c r="N5" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="N5" s="34" t="s">
+      <c r="O5" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="O5" s="34" t="s">
+      <c r="P5" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="P5" s="34" t="s">
+      <c r="Q5" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="Q5" s="34" t="s">
+      <c r="R5" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="R5" s="34" t="s">
+      <c r="S5" s="34" t="s">
         <v>118</v>
-      </c>
-      <c r="S5" s="34" t="s">
-        <v>119</v>
       </c>
       <c r="T5" s="34" t="s">
         <v>104</v>
       </c>
       <c r="U5" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="V5" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="V5" s="34" t="s">
+      <c r="W5" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="X5" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="W5" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="X5" s="34" t="s">
+      <c r="Y5" s="34" t="s">
         <v>122</v>
-      </c>
-      <c r="Y5" s="34" t="s">
-        <v>123</v>
       </c>
       <c r="Z5" s="34" t="s">
         <v>104</v>
       </c>
       <c r="AA5" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB5" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC5" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="AD5" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE5" s="34" t="s">
         <v>124</v>
-      </c>
-      <c r="AB5" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC5" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD5" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="AE5" s="34" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E6" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="F6" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="K6" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="L6" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="M6" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="N6" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="O6" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="P6" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q6" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="R6" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="S6" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="T6" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="U6" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="V6" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="W6" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="X6" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y6" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="H6" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J6" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="K6" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="L6" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="M6" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="N6" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="O6" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="P6" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q6" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="R6" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="S6" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="T6" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="U6" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="V6" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="W6" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="X6" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="Y6" s="34" t="s">
-        <v>130</v>
-      </c>
       <c r="Z6" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AA6" s="34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AB6" s="34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AC6" s="34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AD6" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AE6" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>79</v>
@@ -3241,292 +3056,292 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="P8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="R8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="T8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="U8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="V8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="W8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Y8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Z8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AA8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AB8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AC8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AD8" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AE8" s="34" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="H9" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="I9" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="J9" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="K9" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="L9" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="M9" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="N9" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="C9" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="H9" s="34" t="s">
+      <c r="O9" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="I9" s="34" t="s">
+      <c r="P9" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q9" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="J9" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="K9" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="L9" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="M9" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="N9" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="O9" s="34" t="s">
+      <c r="R9" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="P9" s="34" t="s">
+      <c r="S9" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="Q9" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="R9" s="34" t="s">
+      <c r="T9" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="U9" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="S9" s="34" t="s">
+      <c r="V9" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="W9" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="T9" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="U9" s="34" t="s">
+      <c r="X9" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="V9" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="W9" s="34" t="s">
+      <c r="Y9" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="X9" s="34" t="s">
+      <c r="Z9" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="AA9" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="Y9" s="34" t="s">
+      <c r="AB9" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="AC9" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD9" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="Z9" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA9" s="34" t="s">
+      <c r="AE9" s="34" t="s">
         <v>146</v>
-      </c>
-      <c r="AB9" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="AC9" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="AD9" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="AE9" s="34" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="34" t="s">
         <v>149</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="D10" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="E10" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="F10" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="G10" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="H10" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="J10" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="K10" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="L10" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="M10" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="N10" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="O10" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="P10" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q10" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="R10" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="G10" s="34" t="s">
+      <c r="S10" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="H10" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="I10" s="34" t="s">
+      <c r="T10" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="U10" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="J10" s="34" t="s">
+      <c r="V10" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="W10" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="X10" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y10" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z10" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA10" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB10" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="K10" s="34" t="s">
+      <c r="AC10" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="L10" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="M10" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="N10" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="O10" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="P10" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q10" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="R10" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="S10" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="T10" s="34" t="s">
-        <v>151</v>
-      </c>
-      <c r="U10" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="V10" s="34" t="s">
+      <c r="AD10" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="W10" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="X10" s="34" t="s">
+      <c r="AE10" s="34" t="s">
         <v>159</v>
-      </c>
-      <c r="Y10" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z10" s="34" t="s">
-        <v>151</v>
-      </c>
-      <c r="AA10" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB10" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="AC10" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD10" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="AE10" s="34" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>79</v>
@@ -3538,13 +3353,13 @@
         <v>79</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H11" s="34" t="s">
         <v>79</v>
@@ -3556,25 +3371,25 @@
         <v>79</v>
       </c>
       <c r="K11" s="34" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="M11" s="34" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N11" s="34" t="s">
         <v>79</v>
       </c>
       <c r="O11" s="34" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="P11" s="34" t="s">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="Q11" s="34" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="R11" s="34" t="s">
         <v>79</v>
@@ -3586,13 +3401,13 @@
         <v>79</v>
       </c>
       <c r="U11" s="34" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="V11" s="34" t="s">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="W11" s="34" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="X11" s="34" t="s">
         <v>79</v>
@@ -3604,19 +3419,19 @@
         <v>79</v>
       </c>
       <c r="AA11" s="34" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AB11" s="34" t="s">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="AC11" s="34" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="AD11" s="34" t="s">
         <v>79</v>
       </c>
       <c r="AE11" s="34" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
